--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487961_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487961_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.748900000000001</v>
+        <v>10.1097</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6846</v>
+        <v>7.8489</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0643</v>
+        <v>2.2608</v>
       </c>
       <c r="G2" t="n">
         <v>8.4511</v>
@@ -610,13 +610,13 @@
         <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4871</v>
+        <v>0.848</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3706</v>
+        <v>-0.2063</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8577</v>
+        <v>1.0543</v>
       </c>
       <c r="V2" t="n">
         <v>1.2071</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.5261</v>
+        <v>7.8702</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3763</v>
+        <v>5.58</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1498</v>
+        <v>2.2902</v>
       </c>
       <c r="G3" t="n">
         <v>3.8811</v>
@@ -688,13 +688,13 @@
         <v>3.3698</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2074</v>
+        <v>0.1368</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5578</v>
+        <v>-0.354</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3504</v>
+        <v>0.4908</v>
       </c>
       <c r="V3" t="n">
         <v>1.4737</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.445</v>
+        <v>3.2827</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5839</v>
+        <v>3.6463</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1389</v>
+        <v>-0.3635</v>
       </c>
       <c r="G4" t="n">
         <v>3.4571</v>
@@ -766,13 +766,13 @@
         <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1423</v>
+        <v>0.9801</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0586</v>
+        <v>0.0038</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2009</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-2.3438</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. HASSAN</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.966</v>
+        <v>3.0589</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9053</v>
+        <v>2.6299</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0607</v>
+        <v>0.429</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5013</v>
+        <v>1.289</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5645</v>
+        <v>2.2436</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0633</v>
+        <v>-0.9547</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4457</v>
+        <v>2.6109</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4975</v>
+        <v>2.6433</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0518</v>
+        <v>-0.0324</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0556</v>
+        <v>-1.3219</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.067</v>
+        <v>-0.3996</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0114</v>
+        <v>-0.9223</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4147</v>
+        <v>-0.4194</v>
       </c>
       <c r="T5" t="n">
-        <v>1.351</v>
+        <v>-0.5845</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0636</v>
+        <v>0.1651</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0704</v>
+        <v>0.6036</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>N. KOROL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.67</v>
+        <v>2.1361</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4657</v>
+        <v>1.756</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2044</v>
+        <v>0.3801</v>
       </c>
       <c r="G6" t="n">
-        <v>1.289</v>
+        <v>-0.0314</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2436</v>
+        <v>-1.1983</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9547</v>
+        <v>1.167</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6109</v>
+        <v>0.8791</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6433</v>
+        <v>-0.531</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0324</v>
+        <v>1.4101</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3219</v>
+        <v>-0.9105</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3996</v>
+        <v>-0.6674</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9223</v>
+        <v>-0.2431</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5858</v>
+        <v>0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8083</v>
+        <v>0.4231</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7488</v>
+        <v>0.6609</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0595</v>
+        <v>-0.2378</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6036</v>
+        <v>1.3479</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6036</v>
+        <v>1.2071</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.1408</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3024</v>
+        <v>2.0735</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7191</v>
+        <v>3.8834</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4167</v>
+        <v>-1.8098</v>
       </c>
       <c r="G7" t="n">
         <v>0.5083</v>
@@ -1000,13 +1000,13 @@
         <v>2.1805</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8207</v>
+        <v>0.5919</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2458</v>
+        <v>-0.0815</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0665</v>
+        <v>0.6734</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2071</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. KOROL</t>
+          <t>W. HASSAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3573</v>
+        <v>1.7123</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2861</v>
+        <v>-0.0115</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0712</v>
+        <v>1.7238</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0314</v>
+        <v>-1.5013</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1983</v>
+        <v>-1.5645</v>
       </c>
       <c r="I8" t="n">
-        <v>1.167</v>
+        <v>0.0633</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8791</v>
+        <v>-0.4457</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.531</v>
+        <v>-0.4975</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4101</v>
+        <v>0.0518</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9105</v>
+        <v>-1.0556</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6674</v>
+        <v>-1.067</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2431</v>
+        <v>0.0114</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3964</v>
+        <v>1.9822</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3557</v>
+        <v>1.1609</v>
       </c>
       <c r="T8" t="n">
-        <v>0.191</v>
+        <v>0.4342</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5466</v>
+        <v>0.7267</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3479</v>
+        <v>0.0704</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1408</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5361</v>
+        <v>0.3219</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6236</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.1998</v>
       </c>
       <c r="G9" t="n">
         <v>0.5774</v>
@@ -1156,13 +1156,13 @@
         <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3729</v>
+        <v>0.1588</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0552</v>
+        <v>-0.0467</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3178</v>
+        <v>0.2055</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2071</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS LAJARA</t>
+          <t>R. REQUENA ESCABIAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3367</v>
+        <v>-0.2182</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0422</v>
+        <v>0.0152</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2945</v>
+        <v>-0.2334</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0958</v>
+        <v>-0.1576</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0458</v>
+        <v>-0.6511</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1415</v>
+        <v>0.4935</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0202</v>
+        <v>0.1005</v>
       </c>
       <c r="K12" t="n">
         <v>0.0202</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.0804</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0756</v>
+        <v>-0.2581</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.066</v>
+        <v>-0.6713</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1415</v>
+        <v>0.4132</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4324</v>
+        <v>-0.2588</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0624</v>
+        <v>-0.0853</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.37</v>
+        <v>-0.1735</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. REQUENA ESCABIAS</t>
+          <t>S. TORRECILLAS LAJARA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,55 +1423,55 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4604</v>
+        <v>-0.2805</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0867</v>
+        <v>-0.0422</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3738</v>
+        <v>-0.2383</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1576</v>
+        <v>0.0958</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6511</v>
+        <v>-0.0458</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4935</v>
+        <v>0.1415</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1005</v>
+        <v>0.0202</v>
       </c>
       <c r="K13" t="n">
         <v>0.0202</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0804</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2581</v>
+        <v>0.0756</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6713</v>
+        <v>-0.066</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4132</v>
+        <v>0.1415</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5011</v>
+        <v>-0.3763</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1872</v>
+        <v>-0.0624</v>
       </c>
       <c r="U13" t="n">
         <v>-0.3139</v>
@@ -1501,25 +1501,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>29.8957</v>
+        <v>30.2076</v>
       </c>
       <c r="E14" t="n">
-        <v>24.0707</v>
+        <v>24.3827</v>
       </c>
       <c r="F14" t="n">
-        <v>5.825</v>
+        <v>5.825100000000002</v>
       </c>
       <c r="G14" t="n">
         <v>16.775</v>
       </c>
       <c r="H14" t="n">
-        <v>8.710999999999999</v>
+        <v>8.711</v>
       </c>
       <c r="I14" t="n">
-        <v>8.0641</v>
+        <v>8.064100000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>26.21860000000001</v>
+        <v>26.2186</v>
       </c>
       <c r="K14" t="n">
         <v>15.0156</v>
@@ -1531,10 +1531,10 @@
         <v>-9.443700000000002</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.304699999999999</v>
+        <v>-6.3047</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.139099999999999</v>
+        <v>-3.1391</v>
       </c>
       <c r="P14" t="n">
         <v>9.911200000000001</v>
@@ -1546,16 +1546,16 @@
         <v>19.8224</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6611</v>
+        <v>2.9734</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9532</v>
+        <v>-0.641</v>
       </c>
       <c r="U14" t="n">
         <v>3.6145</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5483</v>
+        <v>0.5483000000000003</v>
       </c>
       <c r="W14" t="n">
         <v>8.7164</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>A. RODRIGUEZ VILLEGAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6445</v>
+        <v>0.0664</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9348</v>
+        <v>1.6963</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2903</v>
+        <v>-1.6298</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.4533</v>
+        <v>1.0115</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.5611</v>
+        <v>-0.9725</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8922</v>
+        <v>1.984</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5315</v>
+        <v>1.2094</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0934</v>
+        <v>-0.6388</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4381</v>
+        <v>1.8482</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.9218</v>
+        <v>-0.1979</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.4676</v>
+        <v>-0.3337</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4542</v>
+        <v>0.1358</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.5769</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6501</v>
+        <v>-0.0046</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4062</v>
+        <v>0.2203</v>
       </c>
       <c r="U15" t="n">
-        <v>2.244</v>
+        <v>-0.2249</v>
       </c>
       <c r="V15" t="n">
-        <v>5.0246</v>
+        <v>-0.9405</v>
       </c>
       <c r="W15" t="n">
-        <v>5.0246</v>
+        <v>0.2666</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ VILLEGAS</t>
+          <t>B. GIMENEZ SALAZAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3691</v>
+        <v>-0.3913</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2888</v>
+        <v>3.0642</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6579</v>
+        <v>-3.4555</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0115</v>
+        <v>0.9489</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9725</v>
+        <v>-0.6447000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1.984</v>
+        <v>1.5936</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2094</v>
+        <v>4.8729</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6388</v>
+        <v>1.6949</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8482</v>
+        <v>3.1779</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1979</v>
+        <v>-3.924</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3337</v>
+        <v>-2.3397</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1358</v>
+        <v>-1.5843</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4401</v>
+        <v>-0.5295</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1872</v>
+        <v>-0.8175</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2529</v>
+        <v>0.288</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9405</v>
+        <v>-1.2071</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>-1.2071</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. GIMENEZ SALAZAR</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0012</v>
+        <v>-0.8356</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7586</v>
+        <v>0.6105</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.7598</v>
+        <v>-1.4461</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9489</v>
+        <v>-4.4533</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-2.5611</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5936</v>
+        <v>-1.8922</v>
       </c>
       <c r="J17" t="n">
-        <v>4.8729</v>
+        <v>-0.5315</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6949</v>
+        <v>-0.0934</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1779</v>
+        <v>-0.4381</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.924</v>
+        <v>-3.9218</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.3397</v>
+        <v>-2.4676</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5843</v>
+        <v>-1.4542</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3964</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R17" t="n">
         <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1394</v>
+        <v>1.17</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1232</v>
+        <v>0.0819</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0163</v>
+        <v>1.0882</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2071</v>
+        <v>5.0246</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>5.0246</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. PEREGRINA FEDOTOV</t>
+          <t>G. CARRAL ESCUDERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2351</v>
+        <v>-1.105</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0333</v>
+        <v>2.5207</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2018</v>
+        <v>-3.6257</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0458</v>
+        <v>-0.1938</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1816</v>
+        <v>-1.535</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1358</v>
+        <v>1.3412</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0202</v>
+        <v>3.1341</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0202</v>
+        <v>1.2781</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.856</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.066</v>
+        <v>-3.3279</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2018</v>
+        <v>-2.8131</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1358</v>
+        <v>-0.5148</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9911</v>
+        <v>0.9911</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1982</v>
+        <v>-0.9617</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0624</v>
+        <v>-0.8799</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1358</v>
+        <v>-0.0818</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. CARRAL ESCUDERO</t>
+          <t>F. PEREGRINA FEDOTOV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7991</v>
+        <v>-1.2351</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2151</v>
+        <v>-1.0333</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.0142</v>
+        <v>-0.2018</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1938</v>
+        <v>-0.0458</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.535</v>
+        <v>-0.1816</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3412</v>
+        <v>0.1358</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1341</v>
+        <v>0.0202</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2781</v>
+        <v>0.0202</v>
       </c>
       <c r="L19" t="n">
-        <v>1.856</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.3279</v>
+        <v>-0.066</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.8131</v>
+        <v>-0.2018</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5148</v>
+        <v>0.1358</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9911</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6559</v>
+        <v>-0.1982</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1855</v>
+        <v>-0.0624</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4703</v>
+        <v>-0.1358</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.854</v>
+        <v>-1.4922</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1489</v>
+        <v>0.1567</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7051</v>
+        <v>-1.649</v>
       </c>
       <c r="G20" t="n">
         <v>-0.633</v>
@@ -2014,13 +2014,13 @@
         <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2122</v>
+        <v>0.1496</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2496</v>
+        <v>0.056</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2071</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>D. DAVID ROCHA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0059</v>
+        <v>-2.9595</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6519</v>
+        <v>-0.581</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6461</v>
+        <v>-2.3785</v>
       </c>
       <c r="G21" t="n">
-        <v>0.189</v>
+        <v>-0.309</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2274</v>
+        <v>-0.9173</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0384</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3698</v>
+        <v>2.4778</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2894</v>
+        <v>1.2245</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0804</v>
+        <v>1.2533</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1807</v>
+        <v>-2.7867</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.062</v>
+        <v>-2.1418</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1187</v>
+        <v>-0.6449</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.5769</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9733</v>
+        <v>-3.9645</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3226</v>
+        <v>-1.349</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3744</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.697</v>
+        <v>-0.7811</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9405</v>
+        <v>1.4737</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.674</v>
+        <v>1.4737</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. YELAMOS MANAS</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3304</v>
+        <v>-3.111</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8208</v>
+        <v>-3.4482</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5096</v>
+        <v>0.3372</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.0268</v>
+        <v>0.189</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6521</v>
+        <v>0.2274</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3747</v>
+        <v>-0.0384</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3139</v>
+        <v>0.3698</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4572</v>
+        <v>0.2894</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8567</v>
+        <v>0.0804</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.7129</v>
+        <v>-0.1807</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.195</v>
+        <v>-0.062</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.518</v>
+        <v>-0.1187</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5947</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6875</v>
+        <v>0.2174</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6647</v>
+        <v>-0.1706</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0229</v>
+        <v>0.3881</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6036</v>
+        <v>-0.9405</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8107</v>
+        <v>-0.674</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. DAVID ROCHA</t>
+          <t>J. YELAMOS MANAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5739</v>
+        <v>-4.1956</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-1.7376</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6874</v>
+        <v>-2.458</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.309</v>
+        <v>-5.0268</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9173</v>
+        <v>-1.6521</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6084000000000001</v>
+        <v>-3.3747</v>
       </c>
       <c r="J23" t="n">
-        <v>2.4778</v>
+        <v>-1.3139</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2245</v>
+        <v>-0.4572</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2533</v>
+        <v>-0.8567</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.7867</v>
+        <v>-3.7129</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.1418</v>
+        <v>-1.195</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6449</v>
+        <v>-2.518</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.7751</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9645</v>
+        <v>-1.9822</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9635</v>
+        <v>0.8223</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8736</v>
+        <v>-0.2522</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.09</v>
+        <v>1.0745</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4737</v>
+        <v>0.6036</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4737</v>
+        <v>1.8107</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2337</v>
+        <v>-6.6663</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4866</v>
+        <v>-1.5884</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.7471</v>
+        <v>-5.0778</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4662</v>
@@ -2326,13 +2326,13 @@
         <v>1.5858</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5604</v>
+        <v>-0.9929</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6936</v>
+        <v>-0.7955</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8668</v>
+        <v>-0.1974</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8107</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.1378</v>
+        <v>-7.2915</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9943</v>
+        <v>-5.485</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1435</v>
+        <v>-1.8065</v>
       </c>
       <c r="G25" t="n">
         <v>-4.7965</v>
@@ -2404,13 +2404,13 @@
         <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1519</v>
+        <v>-0.3056</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.4266</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2159</v>
+        <v>0.121</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6036</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-29.8957</v>
+        <v>-29.2167</v>
       </c>
       <c r="E26" t="n">
         <v>-5.825099999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-24.0706</v>
+        <v>-23.3915</v>
       </c>
       <c r="G26" t="n">
         <v>-16.775</v>
@@ -2482,13 +2482,13 @@
         <v>9.911200000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.6614</v>
+        <v>-1.9822</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.6146</v>
+        <v>-3.6145</v>
       </c>
       <c r="U26" t="n">
-        <v>0.9533000000000005</v>
+        <v>1.6324</v>
       </c>
       <c r="V26" t="n">
         <v>-0.5480999999999999</v>
@@ -2497,7 +2497,7 @@
         <v>8.168200000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.7164</v>
+        <v>-8.716400000000002</v>
       </c>
     </row>
   </sheetData>
